--- a/docs/Logic Requirements/Ageipelago Pachacuti.xlsx
+++ b/docs/Logic Requirements/Ageipelago Pachacuti.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6AF541-8813-4371-937E-E9B91E747065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E272B352-B218-4047-A3B8-3AE6229FE929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Pachacuti" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="219">
   <si>
     <t>Scenario</t>
   </si>
@@ -2396,84 +2396,6 @@
 7 Crossbowmen
 5 Slingers
 2 Mangonels</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>3 Slingers, 1 Chambi Scout
-1 Crossbowman, 3 Elite Skirmishers, 1 Slinger
-4 Crossbowmen, 3 Champi Warriors
-3 Crossbowmen, 2 Slingers, 2 Champi Scouts
-2 Elite Skirmishers, 2 Slingers, 2 Champi Scouts
-2 Elite Skirmishers, 3 Slingers, 2 Champi Scouts
-3 Crossbowmen, 3 Champi Scouts, Misc. Buildings
-3 Kamayuks, 1 Castle
-6 Crossbowmen, 6 Champi Runners, Misc. Buildings
-2 Saboteurs
-(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Scattered Inca Soldiers</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>)
-6 Villagers, Misc. Buildings
-2 Villagers, Misc. Buildings x2
-4 Villagers, Misc. Buildings
-3 Villagers, Misc. Buildings
-1 Villagers, 1 Monk, Misc. Buildings
-2 Onagers, 3 Capped Rams
-(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Locals</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">)
-The Player can build Siege Workshops
-The Player goptains Resources when destroying </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Chanca</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>'s Buildings</t>
     </r>
   </si>
   <si>
@@ -4020,6 +3942,108 @@
 Siege Engineers is researched automatically
 On Moderate and Standard, Bracer is researched automatically
 On Standard, Arbalester, Galleon and Heavy Scorpion are researched automatically</t>
+  </si>
+  <si>
+    <t>Starting Units</t>
+  </si>
+  <si>
+    <t>Starting Buildings</t>
+  </si>
+  <si>
+    <t>Item-Units</t>
+  </si>
+  <si>
+    <t>Item-Buildings</t>
+  </si>
+  <si>
+    <t>Apo Mayta</t>
+  </si>
+  <si>
+    <t>Vicaquirao</t>
+  </si>
+  <si>
+    <t>Pachacuti</t>
+  </si>
+  <si>
+    <r>
+      <t>3 Slingers, 1 Chambi Scout
+1 Crossbowman, 3 Elite Skirmishers, 1 Slinger
+4 Crossbowmen, 3 Champi Warriors
+3 Crossbowmen, 2 Slingers, 2 Champi Scouts
+2 Elite Skirmishers, 2 Slingers, 2 Champi Scouts
+2 Elite Skirmishers, 3 Slingers, 2 Champi Scouts
+3 Crossbowmen, 3 Champi Scouts, Misc. Buildings
+3 Kamayuks, 1 Castle
+6 Crossbowmen, 6 Champi Runners, Misc. Buildings
+2 Saboteurs
+(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Scattered Inca Soldiers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)
+6 Villagers, Misc. Buildings
+2 Villagers, Misc. Buildings x2
+4 Villagers, Misc. Buildings
+3 Villagers, Misc. Buildings
+1 Villagers, 1 Monk, Misc. Buildings
+2 Onagers, 3 Capped Rams
+(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Locals</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+The Player can build Siege Workshops
+The Player optains Resources when destroying </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Chanca</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>'s Buildings</t>
+    </r>
+  </si>
+  <si>
+    <t>Topa Yupanqui</t>
   </si>
 </sst>
 </file>
@@ -4223,7 +4247,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -4383,11 +4407,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4444,9 +4497,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4509,28 +4559,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4567,6 +4596,42 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5049,14 +5114,14 @@
       </c>
       <c r="G6" s="9"/>
       <c r="H6" s="9" t="s">
-        <v>143</v>
+        <v>217</v>
       </c>
       <c r="I6" s="10"/>
       <c r="J6" s="7" t="s">
         <v>35</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>138</v>
@@ -5091,7 +5156,7 @@
         <v>40</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>38</v>
@@ -5101,25 +5166,25 @@
       </c>
       <c r="I7" s="10"/>
       <c r="J7" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="K7" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="L7" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="N7" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="L7" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="M7" s="7" t="s">
+      <c r="O7" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="N7" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="O7" s="7" t="s">
+      <c r="P7" s="7" t="s">
         <v>161</v>
-      </c>
-      <c r="P7" s="7" t="s">
-        <v>162</v>
       </c>
       <c r="Q7" s="7" t="s">
         <v>41</v>
@@ -5133,13 +5198,13 @@
         <v>42</v>
       </c>
       <c r="D8" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="F8" s="9" t="s">
         <v>189</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>190</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>43</v>
@@ -5149,23 +5214,23 @@
       </c>
       <c r="I8" s="10"/>
       <c r="J8" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="K8" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="K8" s="7" t="s">
+      <c r="L8" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="M8" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="M8" s="7" t="s">
+      <c r="N8" s="7" t="s">
         <v>194</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>195</v>
       </c>
       <c r="O8" s="7"/>
       <c r="P8" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q8" s="7" t="s">
         <v>45</v>
@@ -5255,6 +5320,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="7" max="7" width="23.5703125" customWidth="1"/>
     <col min="8" max="8" width="22.5703125" customWidth="1"/>
     <col min="10" max="10" width="12.140625" customWidth="1"/>
@@ -5264,11 +5330,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="43"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="55"/>
       <c r="G2" s="2" t="s">
         <v>47</v>
       </c>
@@ -5283,18 +5349,18 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="45"/>
-      <c r="D3" s="46"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="58"/>
       <c r="G3" s="16" t="s">
         <v>59</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K3" s="27" t="s">
+      <c r="K3" s="26" t="s">
         <v>81</v>
       </c>
       <c r="L3" s="8" t="s">
@@ -5317,7 +5383,7 @@
       <c r="H4" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="24" t="s">
+      <c r="K4" s="23" t="s">
         <v>82</v>
       </c>
       <c r="L4" s="8" t="s">
@@ -5334,13 +5400,13 @@
       <c r="D5" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="G5" s="55" t="s">
+      <c r="G5" s="47" t="s">
         <v>62</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K5" s="24" t="s">
+      <c r="K5" s="23" t="s">
         <v>83</v>
       </c>
       <c r="L5" s="8" t="s">
@@ -5357,14 +5423,14 @@
       <c r="H6" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K6" s="24" t="s">
+      <c r="K6" s="23" t="s">
         <v>84</v>
       </c>
       <c r="L6" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
       <c r="D7" s="19"/>
@@ -5374,24 +5440,33 @@
       <c r="H7" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K7" s="24" t="s">
+      <c r="K7" s="23" t="s">
         <v>85</v>
       </c>
       <c r="L7" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="19"/>
-      <c r="G8" s="24" t="s">
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="G8" s="23" t="s">
         <v>64</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K8" s="24" t="s">
+      <c r="K8" s="23" t="s">
         <v>86</v>
       </c>
       <c r="L8" s="8" t="s">
@@ -5399,16 +5474,21 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="19"/>
-      <c r="G9" s="24" t="s">
+      <c r="B9" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" s="61"/>
+      <c r="E9" s="61"/>
+      <c r="G9" s="23" t="s">
         <v>65</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K9" s="24" t="s">
+      <c r="K9" s="23" t="s">
         <v>87</v>
       </c>
       <c r="L9" s="8" t="s">
@@ -5416,16 +5496,21 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="19"/>
-      <c r="G10" s="24" t="s">
+      <c r="B10" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" s="61"/>
+      <c r="E10" s="61"/>
+      <c r="G10" s="23" t="s">
         <v>67</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K10" s="24" t="s">
+      <c r="K10" s="23" t="s">
         <v>88</v>
       </c>
       <c r="L10" s="8" t="s">
@@ -5433,16 +5518,19 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="19"/>
-      <c r="G11" s="24" t="s">
+      <c r="B11" s="61"/>
+      <c r="C11" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" s="61"/>
+      <c r="E11" s="61"/>
+      <c r="G11" s="23" t="s">
         <v>68</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K11" s="24" t="s">
+      <c r="K11" s="23" t="s">
         <v>89</v>
       </c>
       <c r="L11" s="8" t="s">
@@ -5450,16 +5538,19 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="19"/>
+      <c r="B12" s="61"/>
+      <c r="C12" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
       <c r="G12" s="9" t="s">
         <v>75</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K12" s="24" t="s">
+      <c r="K12" s="23" t="s">
         <v>90</v>
       </c>
       <c r="L12" s="8" t="s">
@@ -5467,16 +5558,17 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="19"/>
-      <c r="G13" s="57" t="s">
+      <c r="B13" s="61"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="61"/>
+      <c r="G13" s="49" t="s">
         <v>70</v>
       </c>
       <c r="H13" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K13" s="24" t="s">
+      <c r="K13" s="23" t="s">
         <v>85</v>
       </c>
       <c r="L13" s="8" t="s">
@@ -5484,16 +5576,17 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="19"/>
-      <c r="G14" s="24" t="s">
+      <c r="B14" s="61"/>
+      <c r="C14" s="61"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
+      <c r="G14" s="23" t="s">
         <v>69</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K14" s="24" t="s">
+      <c r="K14" s="23" t="s">
         <v>91</v>
       </c>
       <c r="L14" s="8" t="s">
@@ -5501,16 +5594,17 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="19"/>
-      <c r="G15" s="24" t="s">
+      <c r="B15" s="61"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="61"/>
+      <c r="G15" s="23" t="s">
         <v>71</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K15" s="24" t="s">
+      <c r="K15" s="23" t="s">
         <v>92</v>
       </c>
       <c r="L15" s="8" t="s">
@@ -5518,169 +5612,202 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="19"/>
-      <c r="G16" s="24" t="s">
+      <c r="B16" s="61"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="61"/>
+      <c r="G16" s="23" t="s">
         <v>72</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K16" s="24" t="s">
+      <c r="K16" s="23" t="s">
         <v>93</v>
       </c>
       <c r="L16" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="61"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="61"/>
       <c r="G17" s="9" t="s">
         <v>74</v>
       </c>
       <c r="H17" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K17" s="24" t="s">
+      <c r="K17" s="23" t="s">
         <v>94</v>
       </c>
       <c r="L17" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="61"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="61"/>
       <c r="G18" s="9" t="s">
         <v>73</v>
       </c>
       <c r="H18" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K18" s="24" t="s">
+      <c r="K18" s="23" t="s">
         <v>95</v>
       </c>
       <c r="L18" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G19" s="25" t="s">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="61"/>
+      <c r="C19" s="61"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="61"/>
+      <c r="G19" s="24" t="s">
         <v>76</v>
       </c>
       <c r="H19" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K19" s="24" t="s">
+      <c r="K19" s="23" t="s">
         <v>96</v>
       </c>
       <c r="L19" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="25" t="s">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="61"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="61"/>
+      <c r="G20" s="24" t="s">
         <v>77</v>
       </c>
       <c r="H20" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K20" s="28" t="s">
+      <c r="K20" s="27" t="s">
         <v>97</v>
       </c>
       <c r="L20" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B21" s="61"/>
+      <c r="C21" s="61"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="61"/>
       <c r="G21" s="9" t="s">
         <v>79</v>
       </c>
       <c r="H21" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K21" s="28" t="s">
+      <c r="K21" s="27" t="s">
         <v>98</v>
       </c>
       <c r="L21" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G22" s="21" t="s">
+    <row r="22" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B22" s="61"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
+      <c r="G22" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="H22" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="K22" s="29" t="s">
+      <c r="H22" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="K22" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="L22" s="22" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="26" t="s">
+      <c r="L22" s="21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="61"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="61"/>
+      <c r="G23" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="H23" s="22" t="s">
+      <c r="H23" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="K23" s="31" t="s">
+      <c r="K23" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="L23" s="22" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="23"/>
-    </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="L23" s="21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="61"/>
+      <c r="C24" s="61"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="61"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
+    </row>
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="14"/>
       <c r="H25" s="14"/>
       <c r="K25" s="14"/>
       <c r="L25" s="14"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="14"/>
       <c r="H26" s="14"/>
       <c r="K26" s="14"/>
       <c r="L26" s="14"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="14"/>
       <c r="H27" s="14"/>
       <c r="K27" s="14"/>
       <c r="L27" s="14"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="14"/>
       <c r="H28" s="14"/>
       <c r="K28" s="14"/>
       <c r="L28" s="14"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="14"/>
       <c r="H29" s="14"/>
       <c r="K29" s="14"/>
       <c r="L29" s="14"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="14"/>
       <c r="H30" s="14"/>
       <c r="K30" s="14"/>
       <c r="L30" s="14"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="14"/>
       <c r="H31" s="14"/>
       <c r="K31" s="14"/>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="14"/>
       <c r="H32" s="14"/>
       <c r="K32" s="19"/>
@@ -5761,6 +5888,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="7" max="7" width="23.5703125" customWidth="1"/>
     <col min="8" max="8" width="22.5703125" customWidth="1"/>
     <col min="10" max="10" width="12.140625" customWidth="1"/>
@@ -5770,11 +5898,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="43"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="55"/>
       <c r="G2" s="2" t="s">
         <v>47</v>
       </c>
@@ -5789,18 +5917,18 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="56" t="s">
         <v>131</v>
       </c>
-      <c r="C3" s="45"/>
-      <c r="D3" s="46"/>
-      <c r="G3" s="33" t="s">
+      <c r="C3" s="57"/>
+      <c r="D3" s="58"/>
+      <c r="G3" s="32" t="s">
         <v>59</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K3" s="27" t="s">
+      <c r="K3" s="26" t="s">
         <v>125</v>
       </c>
       <c r="L3" s="8" t="s">
@@ -5817,13 +5945,13 @@
       <c r="D4" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G4" s="34" t="s">
+      <c r="G4" s="33" t="s">
         <v>120</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="24" t="s">
+      <c r="K4" s="23" t="s">
         <v>83</v>
       </c>
       <c r="L4" s="8" t="s">
@@ -5840,13 +5968,13 @@
       <c r="D5" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="G5" s="35" t="s">
+      <c r="G5" s="34" t="s">
         <v>61</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K5" s="24" t="s">
+      <c r="K5" s="23" t="s">
         <v>84</v>
       </c>
       <c r="L5" s="8" t="s">
@@ -5857,47 +5985,56 @@
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
       <c r="D6" s="19"/>
-      <c r="G6" s="32" t="s">
+      <c r="G6" s="31" t="s">
         <v>67</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K6" s="24" t="s">
+      <c r="K6" s="23" t="s">
         <v>85</v>
       </c>
       <c r="L6" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
       <c r="D7" s="19"/>
-      <c r="G7" s="32" t="s">
+      <c r="G7" s="31" t="s">
         <v>69</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K7" s="24" t="s">
+      <c r="K7" s="23" t="s">
         <v>86</v>
       </c>
       <c r="L7" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="19"/>
-      <c r="G8" s="32" t="s">
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="G8" s="31" t="s">
         <v>77</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K8" s="24" t="s">
+      <c r="K8" s="23" t="s">
         <v>88</v>
       </c>
       <c r="L8" s="8" t="s">
@@ -5905,16 +6042,23 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="19"/>
-      <c r="G9" s="32" t="s">
+      <c r="B9" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="61"/>
+      <c r="D9" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="E9" s="60" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" s="31" t="s">
         <v>76</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K9" s="24" t="s">
+      <c r="K9" s="23" t="s">
         <v>126</v>
       </c>
       <c r="L9" s="8" t="s">
@@ -5922,16 +6066,23 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="19"/>
-      <c r="G10" s="24" t="s">
+      <c r="B10" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="61"/>
+      <c r="D10" s="60" t="s">
+        <v>215</v>
+      </c>
+      <c r="E10" s="60" t="s">
+        <v>84</v>
+      </c>
+      <c r="G10" s="23" t="s">
         <v>112</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K10" s="24" t="s">
+      <c r="K10" s="23" t="s">
         <v>100</v>
       </c>
       <c r="L10" s="8" t="s">
@@ -5939,16 +6090,23 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="19"/>
-      <c r="G11" s="24" t="s">
+      <c r="B11" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" s="61"/>
+      <c r="D11" s="60" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="60" t="s">
+        <v>86</v>
+      </c>
+      <c r="G11" s="23" t="s">
         <v>114</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K11" s="24" t="s">
+      <c r="K11" s="23" t="s">
         <v>95</v>
       </c>
       <c r="L11" s="8" t="s">
@@ -5956,16 +6114,23 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="19"/>
-      <c r="G12" s="24" t="s">
+      <c r="B12" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" s="61"/>
+      <c r="D12" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="60" t="s">
+        <v>89</v>
+      </c>
+      <c r="G12" s="23" t="s">
         <v>72</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K12" s="24" t="s">
+      <c r="K12" s="23" t="s">
         <v>127</v>
       </c>
       <c r="L12" s="8" t="s">
@@ -5973,16 +6138,21 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="19"/>
+      <c r="B13" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="60" t="s">
+        <v>88</v>
+      </c>
       <c r="G13" s="9" t="s">
         <v>113</v>
       </c>
       <c r="H13" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K13" s="37" t="s">
+      <c r="K13" s="36" t="s">
         <v>128</v>
       </c>
       <c r="L13" s="8" t="s">
@@ -5990,16 +6160,19 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="19"/>
-      <c r="G14" s="32" t="s">
+      <c r="B14" s="61"/>
+      <c r="C14" s="61"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="60" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="31" t="s">
         <v>115</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K14" s="32" t="s">
+      <c r="K14" s="31" t="s">
         <v>89</v>
       </c>
       <c r="L14" s="8" t="s">
@@ -6007,16 +6180,19 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="19"/>
-      <c r="G15" s="32" t="s">
+      <c r="B15" s="61"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="60" t="s">
+        <v>92</v>
+      </c>
+      <c r="G15" s="31" t="s">
         <v>116</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K15" s="32" t="s">
+      <c r="K15" s="31" t="s">
         <v>92</v>
       </c>
       <c r="L15" s="8" t="s">
@@ -6024,177 +6200,212 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="19"/>
-      <c r="G16" s="52" t="s">
+      <c r="B16" s="61"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="G16" s="44" t="s">
         <v>117</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K16" s="32" t="s">
+      <c r="K16" s="31" t="s">
         <v>96</v>
       </c>
       <c r="L16" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="61"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="61"/>
       <c r="G17" s="9" t="s">
         <v>118</v>
       </c>
       <c r="H17" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K17" s="32" t="s">
+      <c r="K17" s="31" t="s">
         <v>97</v>
       </c>
       <c r="L17" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="61"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="61"/>
       <c r="G18" s="9" t="s">
         <v>119</v>
       </c>
       <c r="H18" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K18" s="30" t="s">
+      <c r="K18" s="29" t="s">
         <v>81</v>
       </c>
       <c r="L18" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G19" s="36" t="s">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="61"/>
+      <c r="C19" s="61"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="61"/>
+      <c r="G19" s="35" t="s">
         <v>121</v>
       </c>
       <c r="H19" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="K19" s="30" t="s">
+      <c r="K19" s="29" t="s">
         <v>82</v>
       </c>
       <c r="L19" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="58" t="s">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="61"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="61"/>
+      <c r="G20" s="50" t="s">
         <v>122</v>
       </c>
       <c r="H20" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="K20" s="30" t="s">
+      <c r="K20" s="29" t="s">
         <v>90</v>
       </c>
       <c r="L20" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G21" s="36" t="s">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="61"/>
+      <c r="C21" s="61"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="61"/>
+      <c r="G21" s="35" t="s">
         <v>123</v>
       </c>
       <c r="H21" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="K21" s="30" t="s">
+      <c r="K21" s="29" t="s">
         <v>87</v>
       </c>
       <c r="L21" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="31" t="s">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="61"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
+      <c r="G22" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="H22" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="K22" s="31" t="s">
+      <c r="H22" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="K22" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="L22" s="22" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="31" t="s">
+      <c r="L22" s="21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="61"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="61"/>
+      <c r="G23" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="H23" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="K23" s="31" t="s">
+      <c r="H23" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="K23" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="L23" s="22" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="53" t="s">
+      <c r="L23" s="21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="61"/>
+      <c r="C24" s="61"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="61"/>
+      <c r="G24" s="45" t="s">
         <v>136</v>
       </c>
       <c r="H24" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="K24" s="28" t="s">
+      <c r="K24" s="27" t="s">
         <v>129</v>
       </c>
       <c r="L24" s="8" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="14"/>
       <c r="H25" s="14"/>
       <c r="K25" s="14"/>
       <c r="L25" s="14"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="14"/>
       <c r="H26" s="14"/>
       <c r="K26" s="14"/>
       <c r="L26" s="14"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="14"/>
       <c r="H27" s="14"/>
       <c r="K27" s="14"/>
       <c r="L27" s="14"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="14"/>
       <c r="H28" s="14"/>
       <c r="K28" s="14"/>
       <c r="L28" s="14"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="14"/>
       <c r="H29" s="14"/>
       <c r="K29" s="14"/>
       <c r="L29" s="14"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="14"/>
       <c r="H30" s="14"/>
       <c r="K30" s="14"/>
       <c r="L30" s="14"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="14"/>
       <c r="H31" s="14"/>
       <c r="K31" s="14"/>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="14"/>
       <c r="H32" s="14"/>
       <c r="K32" s="19"/>
@@ -6275,6 +6486,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
     <col min="7" max="7" width="23.5703125" customWidth="1"/>
     <col min="8" max="8" width="22.5703125" customWidth="1"/>
     <col min="10" max="10" width="12.140625" customWidth="1"/>
@@ -6284,11 +6496,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="43"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="55"/>
       <c r="G2" s="2" t="s">
         <v>47</v>
       </c>
@@ -6303,18 +6515,18 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="45"/>
-      <c r="D3" s="46"/>
-      <c r="G3" s="33" t="s">
+      <c r="C3" s="57"/>
+      <c r="D3" s="58"/>
+      <c r="G3" s="32" t="s">
         <v>59</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K3" s="38" t="s">
+      <c r="K3" s="37" t="s">
         <v>128</v>
       </c>
       <c r="L3" s="8" t="s">
@@ -6331,13 +6543,13 @@
       <c r="D4" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G4" s="56" t="s">
-        <v>146</v>
+      <c r="G4" s="48" t="s">
+        <v>145</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="24" t="s">
+      <c r="K4" s="23" t="s">
         <v>125</v>
       </c>
       <c r="L4" s="8" t="s">
@@ -6346,21 +6558,21 @@
     </row>
     <row r="5" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
       <c r="B5" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="C5" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="D5" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="D5" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="G5" s="34" t="s">
+      <c r="G5" s="33" t="s">
         <v>61</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K5" s="24" t="s">
+      <c r="K5" s="23" t="s">
         <v>93</v>
       </c>
       <c r="L5" s="8" t="s">
@@ -6371,47 +6583,56 @@
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
       <c r="D6" s="19"/>
-      <c r="G6" s="28" t="s">
-        <v>144</v>
+      <c r="G6" s="27" t="s">
+        <v>143</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K6" s="24" t="s">
+      <c r="K6" s="23" t="s">
         <v>95</v>
       </c>
       <c r="L6" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
       <c r="D7" s="19"/>
-      <c r="G7" s="28" t="s">
+      <c r="G7" s="27" t="s">
         <v>69</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K7" s="24" t="s">
+      <c r="K7" s="23" t="s">
         <v>100</v>
       </c>
       <c r="L7" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="19"/>
-      <c r="G8" s="28" t="s">
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="G8" s="27" t="s">
         <v>76</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K8" s="24" t="s">
+      <c r="K8" s="23" t="s">
         <v>85</v>
       </c>
       <c r="L8" s="8" t="s">
@@ -6419,16 +6640,23 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="19"/>
-      <c r="G9" s="28" t="s">
+      <c r="B9" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="61"/>
+      <c r="D9" s="60" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" s="63" t="s">
+        <v>82</v>
+      </c>
+      <c r="G9" s="27" t="s">
         <v>112</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K9" s="37" t="s">
+      <c r="K9" s="36" t="s">
         <v>96</v>
       </c>
       <c r="L9" s="8" t="s">
@@ -6436,16 +6664,23 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="19"/>
-      <c r="G10" s="28" t="s">
+      <c r="B10" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="61"/>
+      <c r="D10" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="G10" s="27" t="s">
         <v>67</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K10" s="37" t="s">
+      <c r="K10" s="36" t="s">
         <v>126</v>
       </c>
       <c r="L10" s="8" t="s">
@@ -6453,16 +6688,23 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="19"/>
-      <c r="G11" s="28" t="s">
+      <c r="B11" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="61"/>
+      <c r="D11" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="E11" s="63" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" s="27" t="s">
         <v>77</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K11" s="37" t="s">
+      <c r="K11" s="36" t="s">
         <v>81</v>
       </c>
       <c r="L11" s="8" t="s">
@@ -6470,16 +6712,23 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="19"/>
-      <c r="G12" s="24" t="s">
+      <c r="B12" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="61"/>
+      <c r="D12" s="60" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="59" t="s">
+        <v>84</v>
+      </c>
+      <c r="G12" s="23" t="s">
         <v>66</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K12" s="37" t="s">
+      <c r="K12" s="36" t="s">
         <v>88</v>
       </c>
       <c r="L12" s="8" t="s">
@@ -6487,15 +6736,23 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="G13" s="24" t="s">
+      <c r="B13" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="61"/>
+      <c r="D13" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="G13" s="23" t="s">
         <v>71</v>
       </c>
       <c r="H13" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K13" s="37" t="s">
+      <c r="K13" s="36" t="s">
         <v>84</v>
       </c>
       <c r="L13" s="8" t="s">
@@ -6503,15 +6760,23 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="G14" s="37" t="s">
+      <c r="B14" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="C14" s="61"/>
+      <c r="D14" s="60" t="s">
         <v>147</v>
       </c>
+      <c r="E14" s="63" t="s">
+        <v>98</v>
+      </c>
+      <c r="G14" s="36" t="s">
+        <v>146</v>
+      </c>
       <c r="H14" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K14" s="37" t="s">
+      <c r="K14" s="36" t="s">
         <v>83</v>
       </c>
       <c r="L14" s="8" t="s">
@@ -6519,15 +6784,23 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="G15" s="37" t="s">
+      <c r="B15" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="C15" s="61"/>
+      <c r="D15" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="G15" s="36" t="s">
         <v>68</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K15" s="37" t="s">
+      <c r="K15" s="36" t="s">
         <v>86</v>
       </c>
       <c r="L15" s="8" t="s">
@@ -6535,156 +6808,204 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="G16" s="36" t="s">
+      <c r="B16" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="C16" s="61"/>
+      <c r="D16" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16" s="60" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16" s="35" t="s">
         <v>121</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K16" s="54" t="s">
+      <c r="K16" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="61"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="G17" s="35" t="s">
+        <v>123</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K17" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="61"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="60" t="s">
+        <v>86</v>
+      </c>
+      <c r="G18" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="K18" s="46" t="s">
         <v>151</v>
       </c>
-      <c r="L16" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G17" s="36" t="s">
-        <v>123</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K17" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G18" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="K18" s="54" t="s">
-        <v>152</v>
-      </c>
       <c r="L18" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G19" s="39" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="61"/>
+      <c r="C19" s="61"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="G19" s="38" t="s">
+        <v>147</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="K19" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="61"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="G20" s="38" t="s">
         <v>148</v>
       </c>
-      <c r="H19" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="K19" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="39" t="s">
+      <c r="H20" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="H20" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="K20" s="39" t="s">
+      <c r="K20" s="38" t="s">
         <v>82</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G21" s="40" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="61"/>
+      <c r="C21" s="61"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="61"/>
+      <c r="G21" s="39" t="s">
         <v>115</v>
       </c>
-      <c r="H21" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="K21" s="39" t="s">
+      <c r="H21" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="K21" s="38" t="s">
         <v>98</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="K22" s="40" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="61"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="K22" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="L22" s="22" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="L22" s="21" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="61"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="61"/>
       <c r="G23" s="14"/>
       <c r="H23" s="14"/>
-      <c r="K23" s="23"/>
-      <c r="L23" s="23"/>
-    </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
+    </row>
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="61"/>
+      <c r="C24" s="61"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="61"/>
       <c r="G24" s="14"/>
       <c r="H24" s="14"/>
       <c r="K24" s="14"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="14"/>
       <c r="H25" s="14"/>
       <c r="K25" s="14"/>
       <c r="L25" s="14"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="14"/>
       <c r="H26" s="14"/>
       <c r="K26" s="14"/>
       <c r="L26" s="14"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="14"/>
       <c r="H27" s="14"/>
       <c r="K27" s="14"/>
       <c r="L27" s="14"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="14"/>
       <c r="H28" s="14"/>
       <c r="K28" s="14"/>
       <c r="L28" s="14"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="14"/>
       <c r="H29" s="14"/>
       <c r="K29" s="14"/>
       <c r="L29" s="14"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="14"/>
       <c r="H30" s="14"/>
       <c r="K30" s="14"/>
       <c r="L30" s="14"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="14"/>
       <c r="H31" s="14"/>
       <c r="K31" s="14"/>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="14"/>
       <c r="H32" s="14"/>
       <c r="K32" s="19"/>
@@ -6765,6 +7086,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
     <col min="7" max="7" width="23.5703125" customWidth="1"/>
     <col min="8" max="8" width="22.5703125" customWidth="1"/>
     <col min="10" max="10" width="12.140625" customWidth="1"/>
@@ -6774,11 +7096,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="43"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="55"/>
       <c r="G2" s="2" t="s">
         <v>47</v>
       </c>
@@ -6793,18 +7115,18 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="44" t="s">
-        <v>156</v>
-      </c>
-      <c r="C3" s="45"/>
-      <c r="D3" s="46"/>
+      <c r="B3" s="56" t="s">
+        <v>155</v>
+      </c>
+      <c r="C3" s="57"/>
+      <c r="D3" s="58"/>
       <c r="G3" s="16" t="s">
         <v>59</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K3" s="27" t="s">
+      <c r="K3" s="26" t="s">
         <v>95</v>
       </c>
       <c r="L3" s="8" t="s">
@@ -6827,7 +7149,7 @@
       <c r="H4" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="24" t="s">
+      <c r="K4" s="23" t="s">
         <v>127</v>
       </c>
       <c r="L4" s="8" t="s">
@@ -6836,13 +7158,13 @@
     </row>
     <row r="5" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
       <c r="B5" s="17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>53</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>120</v>
@@ -6850,7 +7172,7 @@
       <c r="H5" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K5" s="24" t="s">
+      <c r="K5" s="23" t="s">
         <v>96</v>
       </c>
       <c r="L5" s="8" t="s">
@@ -6861,47 +7183,56 @@
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
       <c r="D6" s="19"/>
-      <c r="G6" s="55" t="s">
-        <v>163</v>
+      <c r="G6" s="47" t="s">
+        <v>162</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K6" s="24" t="s">
+      <c r="K6" s="23" t="s">
         <v>97</v>
       </c>
       <c r="L6" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
       <c r="D7" s="19"/>
-      <c r="G7" s="55" t="s">
-        <v>164</v>
+      <c r="G7" s="47" t="s">
+        <v>163</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K7" s="24" t="s">
+      <c r="K7" s="23" t="s">
         <v>126</v>
       </c>
       <c r="L7" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="19"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>213</v>
+      </c>
       <c r="G8" s="9" t="s">
         <v>63</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K8" s="24" t="s">
+      <c r="K8" s="23" t="s">
         <v>94</v>
       </c>
       <c r="L8" s="8" t="s">
@@ -6909,16 +7240,25 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="19"/>
+      <c r="B9" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="62" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="60" t="s">
+        <v>147</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>99</v>
+      </c>
       <c r="G9" s="9" t="s">
         <v>61</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K9" s="24" t="s">
+      <c r="K9" s="23" t="s">
         <v>83</v>
       </c>
       <c r="L9" s="8" t="s">
@@ -6926,16 +7266,23 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="19"/>
-      <c r="G10" s="24" t="s">
+      <c r="B10" s="60" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" s="59" t="s">
+        <v>175</v>
+      </c>
+      <c r="E10" s="61"/>
+      <c r="G10" s="23" t="s">
         <v>67</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K10" s="24" t="s">
+      <c r="K10" s="23" t="s">
         <v>84</v>
       </c>
       <c r="L10" s="8" t="s">
@@ -6943,16 +7290,19 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="19"/>
-      <c r="G11" s="24" t="s">
+      <c r="B11" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" s="61"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="61"/>
+      <c r="G11" s="23" t="s">
         <v>68</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K11" s="24" t="s">
+      <c r="K11" s="23" t="s">
         <v>85</v>
       </c>
       <c r="L11" s="8" t="s">
@@ -6960,285 +7310,330 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="19"/>
-      <c r="G12" s="24" t="s">
+      <c r="B12" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="C12" s="61"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
+      <c r="G12" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K12" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="61"/>
+      <c r="G13" s="49" t="s">
+        <v>207</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K13" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="61"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
+      <c r="G14" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K14" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="C15" s="61"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="61"/>
+      <c r="G15" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K15" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="61"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="61"/>
+      <c r="G16" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K16" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B17" s="61"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="61"/>
+      <c r="G17" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K17" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="61"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="61"/>
+      <c r="G18" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K18" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B19" s="61"/>
+      <c r="C19" s="61"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="61"/>
+      <c r="G19" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="H12" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K12" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="19"/>
-      <c r="G13" s="57" t="s">
-        <v>208</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K13" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="19"/>
-      <c r="G14" s="24" t="s">
+      <c r="H19" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K19" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="61"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="61"/>
+      <c r="G20" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K20" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="61"/>
+      <c r="C21" s="61"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="61"/>
+      <c r="G21" s="46" t="s">
+        <v>167</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K21" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="61"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
+      <c r="G22" s="51" t="s">
+        <v>168</v>
+      </c>
+      <c r="H22" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="K22" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="L22" s="21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B23" s="61"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="61"/>
+      <c r="G23" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K23" s="45" t="s">
+        <v>179</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="61"/>
+      <c r="C24" s="61"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="61"/>
+      <c r="G24" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K24" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K25" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K26" s="31" t="s">
+        <v>181</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="38" t="s">
+        <v>112</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K27" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="38" t="s">
         <v>201</v>
       </c>
-      <c r="H14" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K14" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="19"/>
-      <c r="G15" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K15" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="19"/>
-      <c r="G16" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K16" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="G17" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K17" s="39" t="s">
-        <v>89</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G18" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K18" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G19" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K19" s="39" t="s">
-        <v>92</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K20" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="L20" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G21" s="54" t="s">
-        <v>168</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K21" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="59" t="s">
-        <v>169</v>
-      </c>
-      <c r="H22" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="K22" s="29" t="s">
-        <v>99</v>
-      </c>
-      <c r="L22" s="22" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="23" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G23" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K23" s="53" t="s">
-        <v>180</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="60" t="s">
-        <v>170</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K24" s="37" t="s">
-        <v>100</v>
-      </c>
-      <c r="L24" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="39" t="s">
-        <v>72</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K25" s="32" t="s">
-        <v>181</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="39" t="s">
-        <v>171</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K26" s="32" t="s">
-        <v>182</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="39" t="s">
-        <v>112</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K27" s="32" t="s">
+      <c r="H28" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K28" s="44" t="s">
         <v>183</v>
       </c>
-      <c r="L27" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G28" s="39" t="s">
-        <v>202</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K28" s="52" t="s">
-        <v>184</v>
-      </c>
       <c r="L28" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G29" s="28" t="s">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="27" t="s">
         <v>65</v>
       </c>
       <c r="H29" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K29" s="47" t="s">
+      <c r="K29" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="L29" s="22" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G30" s="53" t="s">
-        <v>148</v>
+      <c r="L29" s="21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="45" t="s">
+        <v>147</v>
       </c>
       <c r="H30" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K30" s="23"/>
-      <c r="L30" s="23"/>
-    </row>
-    <row r="31" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+    </row>
+    <row r="31" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
       <c r="G31" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>49</v>
@@ -7246,9 +7641,9 @@
       <c r="K31" s="14"/>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G32" s="28" t="s">
-        <v>149</v>
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="27" t="s">
+        <v>148</v>
       </c>
       <c r="H32" s="8" t="s">
         <v>49</v>
@@ -7257,10 +7652,10 @@
       <c r="L32" s="19"/>
     </row>
     <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G33" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="H33" s="22" t="s">
+      <c r="G33" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="H33" s="21" t="s">
         <v>49</v>
       </c>
       <c r="K33" s="19"/>
@@ -7268,7 +7663,7 @@
     </row>
     <row r="34" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G34" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H34" s="8" t="s">
         <v>49</v>
@@ -7277,8 +7672,8 @@
       <c r="L34" s="19"/>
     </row>
     <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G35" s="36" t="s">
-        <v>176</v>
+      <c r="G35" s="35" t="s">
+        <v>175</v>
       </c>
       <c r="H35" s="8" t="s">
         <v>49</v>
@@ -7287,8 +7682,8 @@
       <c r="L35" s="19"/>
     </row>
     <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G36" s="37" t="s">
-        <v>177</v>
+      <c r="G36" s="36" t="s">
+        <v>176</v>
       </c>
       <c r="H36" s="8" t="s">
         <v>49</v>
@@ -7297,18 +7692,18 @@
       <c r="L36" s="19"/>
     </row>
     <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G37" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="H37" s="22" t="s">
+      <c r="G37" s="36" t="s">
+        <v>177</v>
+      </c>
+      <c r="H37" s="21" t="s">
         <v>49</v>
       </c>
       <c r="K37" s="19"/>
       <c r="L37" s="19"/>
     </row>
     <row r="38" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G38" s="37" t="s">
-        <v>179</v>
+      <c r="G38" s="36" t="s">
+        <v>178</v>
       </c>
       <c r="H38" s="8" t="s">
         <v>49</v>
@@ -7360,6 +7755,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="7" max="7" width="23.5703125" customWidth="1"/>
     <col min="8" max="8" width="22.5703125" customWidth="1"/>
     <col min="10" max="10" width="12.140625" customWidth="1"/>
@@ -7369,11 +7765,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="43"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="55"/>
       <c r="G2" s="2" t="s">
         <v>47</v>
       </c>
@@ -7388,18 +7784,18 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="44" t="s">
-        <v>156</v>
-      </c>
-      <c r="C3" s="45"/>
-      <c r="D3" s="46"/>
-      <c r="G3" s="33" t="s">
+      <c r="B3" s="56" t="s">
+        <v>155</v>
+      </c>
+      <c r="C3" s="57"/>
+      <c r="D3" s="58"/>
+      <c r="G3" s="32" t="s">
         <v>59</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K3" s="27" t="s">
+      <c r="K3" s="26" t="s">
         <v>95</v>
       </c>
       <c r="L3" s="8" t="s">
@@ -7416,13 +7812,13 @@
       <c r="D4" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G4" s="34" t="s">
+      <c r="G4" s="33" t="s">
         <v>60</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="24" t="s">
+      <c r="K4" s="23" t="s">
         <v>127</v>
       </c>
       <c r="L4" s="8" t="s">
@@ -7431,22 +7827,22 @@
     </row>
     <row r="5" spans="2:12" ht="262.5" x14ac:dyDescent="0.25">
       <c r="B5" s="17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>53</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>210</v>
-      </c>
-      <c r="G5" s="39" t="s">
+        <v>209</v>
+      </c>
+      <c r="G5" s="38" t="s">
         <v>66</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K5" s="24" t="s">
-        <v>183</v>
+      <c r="K5" s="23" t="s">
+        <v>182</v>
       </c>
       <c r="L5" s="8" t="s">
         <v>49</v>
@@ -7456,379 +7852,465 @@
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
       <c r="D6" s="19"/>
-      <c r="G6" s="39" t="s">
+      <c r="G6" s="38" t="s">
         <v>71</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K6" s="24" t="s">
+      <c r="K6" s="23" t="s">
         <v>83</v>
       </c>
       <c r="L6" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
       <c r="D7" s="19"/>
-      <c r="G7" s="39" t="s">
+      <c r="G7" s="38" t="s">
+        <v>146</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="G8" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="61"/>
+      <c r="D9" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="H7" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K7" s="24" t="s">
+      <c r="E9" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="G9" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K9" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="61"/>
+      <c r="D10" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="60" t="s">
+        <v>82</v>
+      </c>
+      <c r="G10" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K10" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="61"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="G11" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="61"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="60" t="s">
+        <v>98</v>
+      </c>
+      <c r="G12" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K12" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K13" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="C14" s="61"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="60" t="s">
         <v>84</v>
       </c>
-      <c r="L7" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="19"/>
-      <c r="G8" s="39" t="s">
-        <v>69</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K8" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="19"/>
-      <c r="G9" s="39" t="s">
+      <c r="G14" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K14" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="C15" s="61"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="60" t="s">
+        <v>99</v>
+      </c>
+      <c r="G15" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K15" s="27" t="s">
+        <v>180</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="61"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="60" t="s">
+        <v>98</v>
+      </c>
+      <c r="G16" s="27" t="s">
         <v>197</v>
       </c>
-      <c r="H9" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K9" s="24" t="s">
+      <c r="H16" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K16" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B17" s="61"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="60" t="s">
+        <v>89</v>
+      </c>
+      <c r="G17" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K17" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="61"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="60" t="s">
         <v>88</v>
       </c>
-      <c r="L9" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="19"/>
-      <c r="G10" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K10" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="19"/>
-      <c r="G11" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K11" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="19"/>
-      <c r="G12" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K12" s="30" t="s">
-        <v>97</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="19"/>
-      <c r="G13" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K13" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="48"/>
-      <c r="G14" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K14" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="48"/>
-      <c r="G15" s="28" t="s">
+      <c r="G18" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K18" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B19" s="61"/>
+      <c r="C19" s="61"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K19" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="61"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="61"/>
+      <c r="G20" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K20" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="61"/>
+      <c r="C21" s="61"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="61"/>
+      <c r="G21" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K21" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="61"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
+      <c r="G22" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="H22" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="K22" s="44" t="s">
+        <v>203</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B23" s="61"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="61"/>
+      <c r="G23" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K23" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B24" s="61"/>
+      <c r="C24" s="61"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="61"/>
+      <c r="G24" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K24" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G25" s="35" t="s">
+        <v>148</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K25" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="K26" s="42" t="s">
+        <v>205</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="31" t="s">
         <v>200</v>
       </c>
-      <c r="H15" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K15" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="48"/>
-      <c r="G16" s="28" t="s">
-        <v>198</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K16" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="4:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="D17" s="48"/>
-      <c r="G17" s="28" t="s">
-        <v>199</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K17" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="D18" s="48"/>
-      <c r="G18" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K18" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="4:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="D19" s="48"/>
-      <c r="G19" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K19" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K20" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="L20" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G21" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K21" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="49" t="s">
-        <v>147</v>
-      </c>
-      <c r="H22" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="K22" s="52" t="s">
-        <v>204</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="23" spans="4:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G23" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K23" s="32" t="s">
-        <v>94</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="24" spans="4:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G24" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K24" s="47" t="s">
-        <v>98</v>
-      </c>
-      <c r="L24" s="8" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="25" spans="4:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G25" s="36" t="s">
-        <v>149</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K25" s="32" t="s">
-        <v>87</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="26" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="32" t="s">
-        <v>165</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="K26" s="50" t="s">
+      <c r="H27" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="K27" s="43" t="s">
         <v>206</v>
       </c>
-      <c r="L26" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="32" t="s">
+      <c r="L27" s="21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="40" t="s">
         <v>201</v>
       </c>
-      <c r="H27" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="K27" s="51" t="s">
-        <v>207</v>
-      </c>
-      <c r="L27" s="22" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G28" s="47" t="s">
+      <c r="H28" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="H28" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="K28" s="23"/>
-      <c r="L28" s="23"/>
-    </row>
-    <row r="29" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G29" s="32" t="s">
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+    </row>
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="31" t="s">
         <v>80</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K29" s="14"/>
       <c r="L29" s="14"/>
     </row>
-    <row r="30" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="14"/>
       <c r="H30" s="14"/>
       <c r="K30" s="14"/>
       <c r="L30" s="14"/>
     </row>
-    <row r="31" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="14"/>
       <c r="H31" s="14"/>
       <c r="K31" s="14"/>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="14"/>
       <c r="H32" s="14"/>
       <c r="K32" s="19"/>
